--- a/Pinterest-Distribution-Plan-v2.xlsx
+++ b/Pinterest-Distribution-Plan-v2.xlsx
@@ -1669,7 +1669,7 @@
       </c>
       <c r="F2" s="31" t="inlineStr">
         <is>
-          <t>Status (Jun 10)</t>
+          <t>Status (Jun 11)</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F4" s="35" t="inlineStr">
         <is>
-          <t>NOT STARTED — top blocker</t>
+          <t>DONE (Jun 11) — PDF live at /nyc-3-day-itinerary.pdf; NYC_ITINERARY_PDF_URL set in .env.local (verified)</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>DONE (Jun 11) — EmailSignup component live on top NYC landing pages (verified in code)</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>DONE (Jun 11) — per Mridul</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="F16" s="35" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>READY — UTM scheme applied per-pin at creation time; no pins published yet</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="G3" s="31" t="inlineStr">
         <is>
-          <t>Status (as of Jun 10, 2026)</t>
+          <t>Status (as of Jun 11, 2026)</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="G5" s="36" t="inlineStr">
         <is>
-          <t>PARTIAL. Done: business account, domain claimed+verified, Rich Pin metadata (og:type=article on ~50 pages, OG blocks on 7 NYC pages, title bugfix, 10 OG cards w/ logo+Bold font). NOT DONE: deploy of OG work, PDF lead magnet, SafetyWing/Airalo applications, homepage thumbnail fix, UTM scheme. Carry-overs move to Week 2.</t>
+          <t>DONE (Jun 11) — business account, domain claimed+verified, Rich Pins active, PDF lead magnet + email capture live end-to-end</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>STARTS MON JUN 15. Revised: AI agent replaces Fiverr designer for all graphics (decision Jun 10). Must-do this week: DEPLOY pending OG/article changes; ship PDF; apply to affiliate programs; create 8 boards (copy ready); finish profile (avatar+bio+email confirm); 6 pin master templates via agent WITH visual QA gate.</t>
+          <t>IN PROGRESS (ahead of schedule) — 6 master templates built in pin-templates/ and approved Jun 11; 8 keyword boards still pending</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,6 @@
       <c r="J16" s="50" t="n"/>
       <c r="K16" s="50" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="29">
       <c r="A18" s="52" t="inlineStr">
         <is>
